--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507F18C0-7F91-4A30-AD1A-E72E5028EDC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABB9CB9-1610-468D-9A00-1281E76EE662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Archivo</t>
   </si>
@@ -118,6 +118,12 @@
   </si>
   <si>
     <t>que no se cierre la sesion con f5</t>
+  </si>
+  <si>
+    <t>cuando recarga pasa por la panatalla de login no se si eso este bueno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estoy empezando a dudar quesa bueno suar un sigle app aplication quizas sea mejor usar con paginas por si acaso vamos a implemtnarlo mejor evalua si es mejor usarlo puto con algun framwrok ojo que es super importante mantener los principisio de ligerz de ram a nivel de server </t>
   </si>
 </sst>
 </file>
@@ -485,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78774AED-9F48-469B-8E20-962ABD543573}">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -572,72 +578,79 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="M21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="M23" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>23</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ABB9CB9-1610-468D-9A00-1281E76EE662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA7DB80-1BBE-4163-9BB8-38F940E59419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
+    <workbookView xWindow="1500" yWindow="1500" windowWidth="14280" windowHeight="8964" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -508,7 +508,7 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I3" t="s">
@@ -516,7 +516,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>25</v>
       </c>
     </row>
@@ -551,20 +551,22 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
+      <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D12" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
+      <c r="A13" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="1" t="s">
         <v>7</v>
       </c>
     </row>

--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEA7DB80-1BBE-4163-9BB8-38F940E59419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DCB723-619D-411C-A81E-B0D7DE122186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1500" windowWidth="14280" windowHeight="8964" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
@@ -491,7 +491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78774AED-9F48-469B-8E20-962ABD543573}">
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -571,12 +571,12 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
+      <c r="A15" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
@@ -599,11 +599,17 @@
       <c r="A20" t="s">
         <v>14</v>
       </c>
+      <c r="J20" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>15</v>
       </c>
+      <c r="J21" t="s">
+        <v>18</v>
+      </c>
       <c r="M21" t="s">
         <v>31</v>
       </c>
@@ -621,34 +627,22 @@
         <v>32</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="J26" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-    </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+      <c r="A27" s="1" t="s">
         <v>21</v>
+      </c>
+      <c r="J27" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59DCB723-619D-411C-A81E-B0D7DE122186}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A51ABF-D918-4CD9-8FF7-0A870FF63229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1500" windowWidth="14280" windowHeight="8964" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
@@ -526,7 +526,7 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+      <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
     </row>

--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A51ABF-D918-4CD9-8FF7-0A870FF63229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C99C6B-9DB5-4194-9CE0-310DE99AD3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1500" windowWidth="14280" windowHeight="8964" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
@@ -641,7 +641,7 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="A28" s="1" t="s">
         <v>22</v>
       </c>
     </row>

--- a/Pendientes.xlsx
+++ b/Pendientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ciencias-ucv-digital-archive\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C99C6B-9DB5-4194-9CE0-310DE99AD3EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC378614-6472-488D-B35F-BF8E67098E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1500" windowWidth="14280" windowHeight="8964" xr2:uid="{F626A3E1-EC9A-4A32-84C9-ED57EC63FDB0}"/>
   </bookViews>
